--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_150/per_file_predictions_epoch_150.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_150/per_file_predictions_epoch_150.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9487,0.0419,0.0075,0.0015</t>
-  </si>
-  <si>
-    <t>0.9729,0.0085,0.0095,0.0026</t>
-  </si>
-  <si>
-    <t>0.9641,0.0159,0.0082,0.0024</t>
-  </si>
-  <si>
-    <t>0.9774,0.0080,0.0067,0.0016</t>
-  </si>
-  <si>
-    <t>0.8763,0.0979,0.0080,0.0059</t>
-  </si>
-  <si>
-    <t>0.8455,0.0775,0.0072,0.0186</t>
-  </si>
-  <si>
-    <t>0.9645,0.0311,0.0018,0.0009</t>
-  </si>
-  <si>
-    <t>0.9204,0.0847,0.0038,0.0015</t>
-  </si>
-  <si>
-    <t>0.9765,0.0104,0.0026,0.0021</t>
-  </si>
-  <si>
-    <t>0.8463,0.1073,0.0105,0.0121</t>
-  </si>
-  <si>
-    <t>0.9372,0.0392,0.0046,0.0030</t>
-  </si>
-  <si>
-    <t>0.9660,0.0089,0.0043,0.0058</t>
-  </si>
-  <si>
-    <t>0.9877,0.0016,0.0088,0.0002</t>
-  </si>
-  <si>
-    <t>0.9277,0.0461,0.0176,0.0006</t>
-  </si>
-  <si>
-    <t>0.9920,0.0037,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.8226,0.1339,0.0281,0.0003</t>
-  </si>
-  <si>
-    <t>0.9843,0.0064,0.0047,0.0003</t>
-  </si>
-  <si>
-    <t>0.9031,0.1048,0.0028,0.0007</t>
-  </si>
-  <si>
-    <t>0.8435,0.1751,0.0127,0.0014</t>
-  </si>
-  <si>
-    <t>0.6214,0.4181,0.0140,0.0031</t>
-  </si>
-  <si>
-    <t>0.7527,0.2932,0.0086,0.0006</t>
-  </si>
-  <si>
-    <t>0.6426,0.4316,0.0115,0.0011</t>
-  </si>
-  <si>
-    <t>0.9724,0.0051,0.0232,0.0011</t>
-  </si>
-  <si>
-    <t>0.9344,0.0499,0.0082,0.0004</t>
-  </si>
-  <si>
-    <t>0.9779,0.0021,0.0295,0.0004</t>
-  </si>
-  <si>
-    <t>0.9786,0.0061,0.0130,0.0002</t>
-  </si>
-  <si>
-    <t>0.9859,0.0039,0.0099,0.0001</t>
-  </si>
-  <si>
-    <t>0.9856,0.0022,0.0098,0.0006</t>
-  </si>
-  <si>
-    <t>0.9448,0.0099,0.0704,0.0010</t>
-  </si>
-  <si>
-    <t>0.9887,0.0074,0.0035,0.0001</t>
-  </si>
-  <si>
-    <t>0.9818,0.0087,0.0027,0.0008</t>
-  </si>
-  <si>
-    <t>0.1102,0.2001,0.8564,0.0033</t>
-  </si>
-  <si>
-    <t>0.8396,0.2120,0.0074,0.0002</t>
-  </si>
-  <si>
-    <t>0.9730,0.0189,0.0025,0.0011</t>
-  </si>
-  <si>
-    <t>0.9862,0.0086,0.0021,0.0002</t>
-  </si>
-  <si>
-    <t>0.9005,0.1103,0.0090,0.0014</t>
-  </si>
-  <si>
-    <t>0.9604,0.0460,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.4903,0.3685,0.1842,0.0054</t>
-  </si>
-  <si>
-    <t>0.9433,0.0102,0.0769,0.0018</t>
-  </si>
-  <si>
-    <t>0.9643,0.0060,0.0291,0.0028</t>
-  </si>
-  <si>
-    <t>0.9877,0.0007,0.0218,0.0003</t>
-  </si>
-  <si>
-    <t>0.8917,0.0702,0.0317,0.0005</t>
-  </si>
-  <si>
-    <t>0.8465,0.0907,0.0682,0.0009</t>
-  </si>
-  <si>
-    <t>0.9428,0.0090,0.0729,0.0013</t>
-  </si>
-  <si>
-    <t>0.9699,0.0128,0.0086,0.0007</t>
-  </si>
-  <si>
-    <t>0.8753,0.1327,0.0076,0.0006</t>
-  </si>
-  <si>
-    <t>0.6713,0.3993,0.0199,0.0011</t>
-  </si>
-  <si>
-    <t>0.4680,0.6844,0.0069,0.0006</t>
-  </si>
-  <si>
-    <t>0.8718,0.0325,0.1600,0.0016</t>
-  </si>
-  <si>
-    <t>0.8988,0.0094,0.1994,0.0006</t>
-  </si>
-  <si>
-    <t>0.9728,0.0047,0.0200,0.0014</t>
-  </si>
-  <si>
-    <t>0.9576,0.0025,0.0806,0.0005</t>
-  </si>
-  <si>
-    <t>0.7890,0.0112,0.3341,0.0008</t>
-  </si>
-  <si>
-    <t>0.9770,0.0032,0.0263,0.0001</t>
-  </si>
-  <si>
-    <t>0.7684,0.1874,0.0296,0.0126</t>
-  </si>
-  <si>
-    <t>0.9813,0.0088,0.0015,0.0010</t>
-  </si>
-  <si>
-    <t>0.8783,0.0971,0.0039,0.0032</t>
-  </si>
-  <si>
-    <t>0.5174,0.2632,0.3538,0.0075</t>
-  </si>
-  <si>
-    <t>0.9000,0.0376,0.0144,0.0248</t>
-  </si>
-  <si>
-    <t>0.9568,0.0206,0.0043,0.0041</t>
-  </si>
-  <si>
-    <t>0.9163,0.0568,0.0058,0.0063</t>
-  </si>
-  <si>
-    <t>0.0086,0.9149,0.8789,0.0003</t>
-  </si>
-  <si>
-    <t>0.7445,0.0238,0.4301,0.0002</t>
-  </si>
-  <si>
-    <t>0.8882,0.0211,0.1324,0.0023</t>
-  </si>
-  <si>
-    <t>0.0089,0.9112,0.9006,0.0015</t>
-  </si>
-  <si>
-    <t>0.8067,0.0150,0.3070,0.0007</t>
-  </si>
-  <si>
-    <t>0.8313,0.3097,0.0061,0.0002</t>
-  </si>
-  <si>
-    <t>0.2064,0.9040,0.0027,0.0002</t>
-  </si>
-  <si>
-    <t>0.9767,0.0162,0.0060,0.0004</t>
-  </si>
-  <si>
-    <t>0.9930,0.0038,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0737,0.7325,0.5546,0.0033</t>
-  </si>
-  <si>
-    <t>0.7116,0.1405,0.1533,0.0013</t>
-  </si>
-  <si>
-    <t>0.6705,0.1703,0.1845,0.0012</t>
-  </si>
-  <si>
-    <t>0.1333,0.8582,0.1325,0.0006</t>
-  </si>
-  <si>
-    <t>0.0931,0.8506,0.1889,0.0002</t>
-  </si>
-  <si>
-    <t>0.9709,0.0032,0.0244,0.0016</t>
-  </si>
-  <si>
-    <t>0.9636,0.0032,0.0016,0.0150</t>
-  </si>
-  <si>
-    <t>0.9764,0.0039,0.0094,0.0039</t>
-  </si>
-  <si>
-    <t>0.9920,0.0020,0.0029,0.0004</t>
-  </si>
-  <si>
-    <t>0.9876,0.0018,0.0036,0.0017</t>
-  </si>
-  <si>
-    <t>0.9116,0.0260,0.0075,0.0087</t>
-  </si>
-  <si>
-    <t>0.0759,0.8080,0.5081,0.0012</t>
-  </si>
-  <si>
-    <t>0.4610,0.2048,0.4226,0.0031</t>
-  </si>
-  <si>
-    <t>0.5852,0.2704,0.1365,0.0007</t>
-  </si>
-  <si>
-    <t>0.3339,0.3761,0.3737,0.0015</t>
-  </si>
-  <si>
-    <t>0.0605,0.7400,0.6698,0.0005</t>
-  </si>
-  <si>
-    <t>0.4502,0.4159,0.1891,0.0014</t>
-  </si>
-  <si>
-    <t>0.9079,0.0346,0.0077,0.0132</t>
-  </si>
-  <si>
-    <t>0.9259,0.0462,0.0109,0.0071</t>
-  </si>
-  <si>
-    <t>0.8745,0.0746,0.0037,0.0082</t>
-  </si>
-  <si>
-    <t>0.7948,0.1235,0.0302,0.0220</t>
-  </si>
-  <si>
-    <t>0.9675,0.0247,0.0016,0.0013</t>
-  </si>
-  <si>
-    <t>0.8160,0.1465,0.0063,0.0048</t>
-  </si>
-  <si>
-    <t>0.9404,0.0486,0.0066,0.0019</t>
-  </si>
-  <si>
-    <t>0.9329,0.0409,0.0076,0.0037</t>
-  </si>
-  <si>
-    <t>0.9391,0.0350,0.0018,0.0046</t>
-  </si>
-  <si>
-    <t>0.8171,0.0704,0.0175,0.0251</t>
-  </si>
-  <si>
-    <t>0.9302,0.0250,0.0061,0.0154</t>
-  </si>
-  <si>
-    <t>0.8868,0.0472,0.0119,0.0153</t>
-  </si>
-  <si>
-    <t>0.8042,0.1124,0.0147,0.0169</t>
-  </si>
-  <si>
-    <t>0.8883,0.0826,0.0115,0.0057</t>
-  </si>
-  <si>
-    <t>0.9092,0.0685,0.0030,0.0047</t>
-  </si>
-  <si>
-    <t>0.9682,0.0097,0.0072,0.0055</t>
-  </si>
-  <si>
-    <t>0.8163,0.0217,0.2772,0.0009</t>
-  </si>
-  <si>
-    <t>0.8985,0.0198,0.1198,0.0010</t>
-  </si>
-  <si>
-    <t>0.9931,0.0007,0.0037,0.0003</t>
-  </si>
-  <si>
-    <t>0.9673,0.0125,0.0134,0.0003</t>
-  </si>
-  <si>
-    <t>0.4893,0.5919,0.0101,0.0010</t>
-  </si>
-  <si>
-    <t>0.5498,0.5656,0.0029,0.0005</t>
-  </si>
-  <si>
-    <t>0.7185,0.3652,0.0104,0.0006</t>
-  </si>
-  <si>
-    <t>0.9060,0.1384,0.0055,0.0003</t>
-  </si>
-  <si>
-    <t>0.3939,0.6628,0.0061,0.0016</t>
-  </si>
-  <si>
-    <t>0.0106,0.9881,0.0027,0.0013</t>
-  </si>
-  <si>
-    <t>0.8976,0.1293,0.0048,0.0008</t>
-  </si>
-  <si>
-    <t>0.9779,0.0080,0.0080,0.0005</t>
-  </si>
-  <si>
-    <t>0.9839,0.0046,0.0098,0.0003</t>
-  </si>
-  <si>
-    <t>0.9722,0.0059,0.0182,0.0008</t>
-  </si>
-  <si>
-    <t>0.9576,0.0076,0.0403,0.0006</t>
-  </si>
-  <si>
-    <t>0.9841,0.0071,0.0032,0.0005</t>
-  </si>
-  <si>
-    <t>0.9722,0.0380,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.6969,0.4136,0.0061,0.0010</t>
-  </si>
-  <si>
-    <t>0.8913,0.1095,0.0096,0.0014</t>
-  </si>
-  <si>
-    <t>0.1636,0.7035,0.2626,0.0027</t>
-  </si>
-  <si>
-    <t>0.9276,0.0884,0.0023,0.0007</t>
-  </si>
-  <si>
-    <t>0.9222,0.0897,0.0086,0.0016</t>
-  </si>
-  <si>
-    <t>0.9155,0.1228,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.9628,0.0356,0.0049,0.0009</t>
-  </si>
-  <si>
-    <t>0.8684,0.0598,0.0198,0.0214</t>
-  </si>
-  <si>
-    <t>0.9005,0.0632,0.0033,0.0036</t>
-  </si>
-  <si>
-    <t>0.9248,0.0399,0.0057,0.0078</t>
-  </si>
-  <si>
-    <t>0.8931,0.0662,0.0144,0.0171</t>
-  </si>
-  <si>
-    <t>0.9311,0.0683,0.0098,0.0032</t>
-  </si>
-  <si>
-    <t>0.9000,0.0487,0.0048,0.0071</t>
-  </si>
-  <si>
-    <t>0.9512,0.0398,0.0035,0.0010</t>
-  </si>
-  <si>
-    <t>0.2248,0.7135,0.1529,0.0006</t>
-  </si>
-  <si>
-    <t>0.0120,0.9412,0.7603,0.0018</t>
-  </si>
-  <si>
-    <t>0.6033,0.1877,0.2138,0.0011</t>
-  </si>
-  <si>
-    <t>0.9199,0.0489,0.0247,0.0003</t>
-  </si>
-  <si>
-    <t>0.9671,0.0104,0.0139,0.0011</t>
-  </si>
-  <si>
-    <t>0.9751,0.0053,0.0160,0.0003</t>
-  </si>
-  <si>
-    <t>0.9296,0.0293,0.0432,0.0012</t>
-  </si>
-  <si>
-    <t>0.9899,0.0045,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9604,0.0038,0.0243,0.0052</t>
-  </si>
-  <si>
-    <t>0.9562,0.0058,0.0230,0.0064</t>
-  </si>
-  <si>
-    <t>0.9557,0.0049,0.0325,0.0045</t>
-  </si>
-  <si>
-    <t>0.9744,0.0031,0.0185,0.0025</t>
-  </si>
-  <si>
-    <t>0.2131,0.5500,0.5365,0.0101</t>
-  </si>
-  <si>
-    <t>0.9093,0.0471,0.0040,0.0076</t>
-  </si>
-  <si>
-    <t>0.9130,0.0710,0.0066,0.0020</t>
-  </si>
-  <si>
-    <t>0.9670,0.0128,0.0026,0.0030</t>
-  </si>
-  <si>
-    <t>0.9304,0.0631,0.0074,0.0018</t>
-  </si>
-  <si>
-    <t>0.9383,0.0410,0.0188,0.0038</t>
-  </si>
-  <si>
-    <t>0.9729,0.0095,0.0072,0.0008</t>
-  </si>
-  <si>
-    <t>0.8728,0.0949,0.0131,0.0068</t>
-  </si>
-  <si>
-    <t>0.2213,0.4827,0.6187,0.0355</t>
-  </si>
-  <si>
-    <t>0.8744,0.0982,0.0172,0.0039</t>
-  </si>
-  <si>
-    <t>0.9816,0.0083,0.0035,0.0007</t>
-  </si>
-  <si>
-    <t>0.9244,0.0839,0.0053,0.0007</t>
-  </si>
-  <si>
-    <t>0.9584,0.0356,0.0028,0.0008</t>
-  </si>
-  <si>
-    <t>0.9920,0.0031,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.8868,0.1065,0.0146,0.0017</t>
-  </si>
-  <si>
-    <t>0.9752,0.0140,0.0104,0.0005</t>
-  </si>
-  <si>
-    <t>0.9601,0.0428,0.0032,0.0008</t>
-  </si>
-  <si>
-    <t>0.9677,0.0191,0.0025,0.0018</t>
-  </si>
-  <si>
-    <t>0.8938,0.0521,0.0100,0.0144</t>
-  </si>
-  <si>
-    <t>0.9211,0.0629,0.0064,0.0030</t>
-  </si>
-  <si>
-    <t>0.9275,0.0497,0.0051,0.0046</t>
-  </si>
-  <si>
-    <t>0.9570,0.0324,0.0061,0.0028</t>
-  </si>
-  <si>
-    <t>0.9491,0.0229,0.0050,0.0029</t>
-  </si>
-  <si>
-    <t>0.9127,0.0433,0.0057,0.0067</t>
-  </si>
-  <si>
-    <t>0.9520,0.0329,0.0033,0.0022</t>
-  </si>
-  <si>
-    <t>0.9245,0.0870,0.0020,0.0008</t>
-  </si>
-  <si>
-    <t>0.9018,0.0927,0.0065,0.0014</t>
-  </si>
-  <si>
-    <t>0.8163,0.2575,0.0024,0.0007</t>
-  </si>
-  <si>
-    <t>0.9601,0.0180,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.8735,0.0972,0.0107,0.0054</t>
-  </si>
-  <si>
-    <t>0.9687,0.0115,0.0040,0.0027</t>
-  </si>
-  <si>
-    <t>0.8423,0.1041,0.0116,0.0164</t>
-  </si>
-  <si>
-    <t>0.9566,0.0231,0.0060,0.0032</t>
-  </si>
-  <si>
-    <t>0.0173,0.8327,0.7869,0.0025</t>
-  </si>
-  <si>
-    <t>0.8881,0.0911,0.0177,0.0037</t>
-  </si>
-  <si>
-    <t>0.3519,0.2499,0.2505,0.0012</t>
-  </si>
-  <si>
-    <t>0.9788,0.0066,0.0102,0.0003</t>
-  </si>
-  <si>
-    <t>0.9697,0.0090,0.0141,0.0010</t>
-  </si>
-  <si>
-    <t>0.1629,0.2933,0.7512,0.0009</t>
-  </si>
-  <si>
-    <t>0.9141,0.0275,0.0444,0.0005</t>
-  </si>
-  <si>
-    <t>0.8893,0.0365,0.0616,0.0010</t>
-  </si>
-  <si>
-    <t>0.9054,0.0098,0.1458,0.0005</t>
-  </si>
-  <si>
-    <t>0.9725,0.0079,0.0224,0.0005</t>
-  </si>
-  <si>
-    <t>0.9772,0.0098,0.0078,0.0011</t>
-  </si>
-  <si>
-    <t>0.9439,0.0261,0.0177,0.0029</t>
-  </si>
-  <si>
-    <t>0.8642,0.0967,0.0122,0.0022</t>
-  </si>
-  <si>
-    <t>0.9805,0.0140,0.0042,0.0002</t>
-  </si>
-  <si>
-    <t>0.9803,0.0086,0.0037,0.0006</t>
-  </si>
-  <si>
-    <t>0.9752,0.0084,0.0154,0.0005</t>
-  </si>
-  <si>
-    <t>0.9893,0.0046,0.0027,0.0002</t>
-  </si>
-  <si>
-    <t>0.8855,0.0649,0.0194,0.0086</t>
-  </si>
-  <si>
-    <t>0.9177,0.1013,0.0020,0.0008</t>
-  </si>
-  <si>
-    <t>0.9119,0.0764,0.0056,0.0019</t>
-  </si>
-  <si>
-    <t>0.8227,0.1440,0.0074,0.0062</t>
-  </si>
-  <si>
-    <t>0.9260,0.0598,0.0067,0.0037</t>
-  </si>
-  <si>
-    <t>0.9891,0.0040,0.0029,0.0003</t>
-  </si>
-  <si>
-    <t>0.9852,0.0064,0.0048,0.0002</t>
-  </si>
-  <si>
-    <t>0.9857,0.0028,0.0063,0.0003</t>
-  </si>
-  <si>
-    <t>0.9556,0.0114,0.0366,0.0015</t>
-  </si>
-  <si>
-    <t>0.9631,0.0087,0.0267,0.0011</t>
-  </si>
-  <si>
-    <t>0.7745,0.0349,0.2670,0.0019</t>
-  </si>
-  <si>
-    <t>0.8230,0.0906,0.0718,0.0040</t>
-  </si>
-  <si>
-    <t>0.9433,0.0172,0.0371,0.0033</t>
-  </si>
-  <si>
-    <t>0.5235,0.1787,0.3192,0.0052</t>
-  </si>
-  <si>
-    <t>0.6814,0.0715,0.3550,0.0083</t>
-  </si>
-  <si>
-    <t>0.8703,0.0946,0.0110,0.0079</t>
-  </si>
-  <si>
-    <t>0.9094,0.0577,0.0070,0.0070</t>
-  </si>
-  <si>
-    <t>0.8523,0.1440,0.0128,0.0029</t>
-  </si>
-  <si>
-    <t>0.9079,0.0795,0.0089,0.0042</t>
-  </si>
-  <si>
-    <t>0.9401,0.0506,0.0039,0.0025</t>
-  </si>
-  <si>
-    <t>0.7445,0.2266,0.0220,0.0101</t>
-  </si>
-  <si>
-    <t>0.9045,0.0667,0.0097,0.0082</t>
-  </si>
-  <si>
-    <t>0.9330,0.0375,0.0033,0.0054</t>
-  </si>
-  <si>
-    <t>0.9480,0.0246,0.0271,0.0012</t>
-  </si>
-  <si>
-    <t>0.9729,0.0152,0.0084,0.0007</t>
-  </si>
-  <si>
-    <t>0.9187,0.0620,0.0168,0.0016</t>
-  </si>
-  <si>
-    <t>0.0787,0.4332,0.8003,0.0016</t>
-  </si>
-  <si>
-    <t>0.7405,0.0709,0.2644,0.0078</t>
-  </si>
-  <si>
-    <t>0.8533,0.0396,0.1119,0.0005</t>
-  </si>
-  <si>
-    <t>0.4440,0.1832,0.4086,0.0025</t>
-  </si>
-  <si>
-    <t>0.9954,0.0010,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.2958,0.1332,0.7080,0.0022</t>
-  </si>
-  <si>
-    <t>0.8926,0.0332,0.0710,0.0006</t>
-  </si>
-  <si>
-    <t>0.8775,0.0717,0.0297,0.0011</t>
-  </si>
-  <si>
-    <t>0.9884,0.0014,0.0082,0.0006</t>
-  </si>
-  <si>
-    <t>0.9904,0.0014,0.0085,0.0003</t>
-  </si>
-  <si>
-    <t>0.9964,0.0005,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.8927,0.0641,0.0073,0.0079</t>
-  </si>
-  <si>
-    <t>0.7712,0.1505,0.0070,0.0082</t>
-  </si>
-  <si>
-    <t>0.9232,0.0445,0.0150,0.0121</t>
-  </si>
-  <si>
-    <t>0.7791,0.2310,0.0092,0.0034</t>
-  </si>
-  <si>
-    <t>0.9078,0.0407,0.0040,0.0069</t>
-  </si>
-  <si>
-    <t>0.9264,0.0208,0.0073,0.0163</t>
-  </si>
-  <si>
-    <t>0.9015,0.0737,0.0085,0.0065</t>
-  </si>
-  <si>
-    <t>0.9224,0.0620,0.0054,0.0048</t>
-  </si>
-  <si>
-    <t>0.7237,0.1663,0.0585,0.0004</t>
-  </si>
-  <si>
-    <t>0.4058,0.1169,0.5074,0.0011</t>
-  </si>
-  <si>
-    <t>0.9030,0.0182,0.1119,0.0013</t>
-  </si>
-  <si>
-    <t>0.9359,0.0126,0.0613,0.0006</t>
-  </si>
-  <si>
-    <t>0.8568,0.0071,0.2691,0.0005</t>
-  </si>
-  <si>
-    <t>0.9813,0.0041,0.0111,0.0003</t>
-  </si>
-  <si>
-    <t>0.9678,0.0095,0.0177,0.0011</t>
-  </si>
-  <si>
-    <t>0.9220,0.0162,0.0871,0.0029</t>
-  </si>
-  <si>
-    <t>0.9934,0.0011,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.9575,0.0172,0.0088,0.0038</t>
-  </si>
-  <si>
-    <t>0.9837,0.0027,0.0057,0.0017</t>
-  </si>
-  <si>
-    <t>0.9918,0.0008,0.0030,0.0007</t>
-  </si>
-  <si>
-    <t>0.9583,0.0035,0.0155,0.0119</t>
-  </si>
-  <si>
-    <t>0.9812,0.0111,0.0028,0.0005</t>
+    <t>0.9154,0.0390,0.0014,0.0262</t>
+  </si>
+  <si>
+    <t>0.0645,0.0026,0.0029,0.9685</t>
+  </si>
+  <si>
+    <t>0.8334,0.0055,0.0175,0.1307</t>
+  </si>
+  <si>
+    <t>0.0669,0.0012,0.0016,0.9725</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9910,0.0017,0.0005,0.0034</t>
+  </si>
+  <si>
+    <t>0.9981,0.0006,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9937,0.0022,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9961,0.0012,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9963,0.0009,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9493,0.0070,0.0564,0.0010</t>
+  </si>
+  <si>
+    <t>0.5055,0.0026,0.6613,0.0003</t>
+  </si>
+  <si>
+    <t>0.7546,0.0026,0.4710,0.0006</t>
+  </si>
+  <si>
+    <t>0.0552,0.0394,0.9004,0.0050</t>
+  </si>
+  <si>
+    <t>0.9641,0.0023,0.0531,0.0008</t>
+  </si>
+  <si>
+    <t>0.0107,0.9852,0.0023,0.0026</t>
+  </si>
+  <si>
+    <t>0.0157,0.9812,0.0027,0.0019</t>
+  </si>
+  <si>
+    <t>0.0479,0.9617,0.0017,0.0014</t>
+  </si>
+  <si>
+    <t>0.0545,0.9606,0.0026,0.0010</t>
+  </si>
+  <si>
+    <t>0.0139,0.9854,0.0016,0.0007</t>
+  </si>
+  <si>
+    <t>0.8459,0.0023,0.3195,0.0010</t>
+  </si>
+  <si>
+    <t>0.2795,0.0122,0.7138,0.0144</t>
+  </si>
+  <si>
+    <t>0.0040,0.0051,0.9866,0.0060</t>
+  </si>
+  <si>
+    <t>0.1336,0.0056,0.8772,0.0055</t>
+  </si>
+  <si>
+    <t>0.0140,0.0117,0.9763,0.0029</t>
+  </si>
+  <si>
+    <t>0.0834,0.0046,0.9203,0.0074</t>
+  </si>
+  <si>
+    <t>0.0033,0.0023,0.9868,0.0129</t>
+  </si>
+  <si>
+    <t>0.2539,0.7934,0.0125,0.0023</t>
+  </si>
+  <si>
+    <t>0.5567,0.0952,0.4586,0.0212</t>
+  </si>
+  <si>
+    <t>0.0021,0.0050,0.9926,0.0065</t>
+  </si>
+  <si>
+    <t>0.0370,0.4688,0.4577,0.0060</t>
+  </si>
+  <si>
+    <t>0.9362,0.0580,0.0068,0.0068</t>
+  </si>
+  <si>
+    <t>0.9620,0.0051,0.0292,0.0030</t>
+  </si>
+  <si>
+    <t>0.5075,0.6219,0.0112,0.0010</t>
+  </si>
+  <si>
+    <t>0.0098,0.9819,0.0933,0.0005</t>
+  </si>
+  <si>
+    <t>0.0053,0.9588,0.0216,0.0090</t>
+  </si>
+  <si>
+    <t>0.7425,0.0016,0.2990,0.0116</t>
+  </si>
+  <si>
+    <t>0.2613,0.0085,0.8151,0.0036</t>
+  </si>
+  <si>
+    <t>0.0164,0.0020,0.7761,0.2505</t>
+  </si>
+  <si>
+    <t>0.0051,0.0153,0.9864,0.0018</t>
+  </si>
+  <si>
+    <t>0.0225,0.9219,0.0344,0.0015</t>
+  </si>
+  <si>
+    <t>0.0049,0.0079,0.9886,0.0007</t>
+  </si>
+  <si>
+    <t>0.0977,0.7727,0.0437,0.3823</t>
+  </si>
+  <si>
+    <t>0.0089,0.9851,0.0069,0.0048</t>
+  </si>
+  <si>
+    <t>0.0087,0.9521,0.1033,0.0029</t>
+  </si>
+  <si>
+    <t>0.0012,0.9958,0.0131,0.0008</t>
+  </si>
+  <si>
+    <t>0.0363,0.0371,0.9569,0.0066</t>
+  </si>
+  <si>
+    <t>0.0018,0.0180,0.9930,0.0029</t>
+  </si>
+  <si>
+    <t>0.0182,0.0013,0.9804,0.0021</t>
+  </si>
+  <si>
+    <t>0.0177,0.0016,0.9859,0.0009</t>
+  </si>
+  <si>
+    <t>0.0052,0.0500,0.9907,0.0006</t>
+  </si>
+  <si>
+    <t>0.0237,0.1330,0.9482,0.0035</t>
+  </si>
+  <si>
+    <t>0.9545,0.0926,0.0012,0.0008</t>
+  </si>
+  <si>
+    <t>0.9859,0.0098,0.0023,0.0017</t>
+  </si>
+  <si>
+    <t>0.9913,0.0031,0.0009,0.0026</t>
+  </si>
+  <si>
+    <t>0.0026,0.0414,0.9898,0.0072</t>
+  </si>
+  <si>
+    <t>0.9867,0.0058,0.0046,0.0023</t>
+  </si>
+  <si>
+    <t>0.9945,0.0043,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9665,0.0270,0.0097,0.0035</t>
+  </si>
+  <si>
+    <t>0.0029,0.7978,0.9651,0.0006</t>
+  </si>
+  <si>
+    <t>0.0128,0.0699,0.9874,0.0010</t>
+  </si>
+  <si>
+    <t>0.0466,0.0027,0.9756,0.0011</t>
+  </si>
+  <si>
+    <t>0.0061,0.7858,0.8218,0.0006</t>
+  </si>
+  <si>
+    <t>0.0035,0.0078,0.9884,0.0043</t>
+  </si>
+  <si>
+    <t>0.1326,0.8908,0.0144,0.0051</t>
+  </si>
+  <si>
+    <t>0.0759,0.9720,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9529,0.0080,0.0786,0.0036</t>
+  </si>
+  <si>
+    <t>0.6914,0.1484,0.1921,0.0021</t>
+  </si>
+  <si>
+    <t>0.0051,0.1701,0.9728,0.0036</t>
+  </si>
+  <si>
+    <t>0.0036,0.5965,0.9287,0.0003</t>
+  </si>
+  <si>
+    <t>0.0030,0.6340,0.9516,0.0010</t>
+  </si>
+  <si>
+    <t>0.0046,0.9887,0.0300,0.0005</t>
+  </si>
+  <si>
+    <t>0.0021,0.7940,0.9662,0.0008</t>
+  </si>
+  <si>
+    <t>0.0101,0.0003,0.0150,0.9847</t>
+  </si>
+  <si>
+    <t>0.0035,0.0003,0.0002,0.9984</t>
+  </si>
+  <si>
+    <t>0.0075,0.0010,0.0024,0.9950</t>
+  </si>
+  <si>
+    <t>0.0256,0.0006,0.0480,0.9459</t>
+  </si>
+  <si>
+    <t>0.0027,0.0011,0.0131,0.9951</t>
+  </si>
+  <si>
+    <t>0.0079,0.0062,0.0034,0.9928</t>
+  </si>
+  <si>
+    <t>0.0003,0.9527,0.9656,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.8602,0.9393,0.0005</t>
+  </si>
+  <si>
+    <t>0.0086,0.8197,0.8410,0.0042</t>
+  </si>
+  <si>
+    <t>0.0031,0.5342,0.9446,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.9074,0.9294,0.0001</t>
+  </si>
+  <si>
+    <t>0.0059,0.7283,0.6898,0.0004</t>
+  </si>
+  <si>
+    <t>0.9965,0.0009,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9979,0.0012,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0019,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9952,0.0013,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9965,0.0016,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9935,0.0026,0.0018,0.0014</t>
+  </si>
+  <si>
+    <t>0.9964,0.0023,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0011,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0001,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9970,0.0013,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9975,0.0001,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9971,0.0011,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9980,0.0007,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9959,0.0010,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0173,0.0018,0.9854,0.0018</t>
+  </si>
+  <si>
+    <t>0.0218,0.0940,0.9379,0.0058</t>
+  </si>
+  <si>
+    <t>0.9317,0.0168,0.0327,0.0135</t>
+  </si>
+  <si>
+    <t>0.1421,0.0168,0.8750,0.0045</t>
+  </si>
+  <si>
+    <t>0.0489,0.9628,0.0014,0.0011</t>
+  </si>
+  <si>
+    <t>0.0811,0.9490,0.0016,0.0004</t>
+  </si>
+  <si>
+    <t>0.0271,0.9711,0.0005,0.0060</t>
+  </si>
+  <si>
+    <t>0.1324,0.9179,0.0034,0.0009</t>
+  </si>
+  <si>
+    <t>0.1083,0.9207,0.0032,0.0018</t>
+  </si>
+  <si>
+    <t>0.0103,0.9827,0.0078,0.0009</t>
+  </si>
+  <si>
+    <t>0.9721,0.0576,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.8802,0.0139,0.1598,0.0069</t>
+  </si>
+  <si>
+    <t>0.2490,0.0236,0.7485,0.0107</t>
+  </si>
+  <si>
+    <t>0.3404,0.1509,0.5659,0.0192</t>
+  </si>
+  <si>
+    <t>0.4634,0.0184,0.5806,0.0112</t>
+  </si>
+  <si>
+    <t>0.3965,0.0573,0.3620,0.3000</t>
+  </si>
+  <si>
+    <t>0.0075,0.9879,0.0065,0.0013</t>
+  </si>
+  <si>
+    <t>0.0007,0.9962,0.0014,0.0020</t>
+  </si>
+  <si>
+    <t>0.0116,0.9750,0.0103,0.0233</t>
+  </si>
+  <si>
+    <t>0.0089,0.9629,0.1032,0.0018</t>
+  </si>
+  <si>
+    <t>0.0109,0.9894,0.0071,0.0001</t>
+  </si>
+  <si>
+    <t>0.5675,0.4849,0.0461,0.0029</t>
+  </si>
+  <si>
+    <t>0.8590,0.1876,0.0083,0.0004</t>
+  </si>
+  <si>
+    <t>0.9707,0.0278,0.0141,0.0025</t>
+  </si>
+  <si>
+    <t>0.9956,0.0005,0.0010,0.0015</t>
+  </si>
+  <si>
+    <t>0.9953,0.0008,0.0006,0.0018</t>
+  </si>
+  <si>
+    <t>0.9892,0.0077,0.0032,0.0012</t>
+  </si>
+  <si>
+    <t>0.9972,0.0004,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9963,0.0022,0.0018,0.0002</t>
+  </si>
+  <si>
+    <t>0.9851,0.0024,0.0033,0.0077</t>
+  </si>
+  <si>
+    <t>0.9879,0.0033,0.0033,0.0034</t>
+  </si>
+  <si>
+    <t>0.0125,0.6839,0.7982,0.0042</t>
+  </si>
+  <si>
+    <t>0.0071,0.2409,0.9571,0.0002</t>
+  </si>
+  <si>
+    <t>0.0093,0.0843,0.9700,0.0020</t>
+  </si>
+  <si>
+    <t>0.0082,0.0753,0.9851,0.0005</t>
+  </si>
+  <si>
+    <t>0.9927,0.0014,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.8949,0.0145,0.0790,0.0060</t>
+  </si>
+  <si>
+    <t>0.5664,0.0026,0.6812,0.0012</t>
+  </si>
+  <si>
+    <t>0.8472,0.0721,0.0858,0.0036</t>
+  </si>
+  <si>
+    <t>0.0531,0.0019,0.0105,0.9661</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.0032,0.9990</t>
+  </si>
+  <si>
+    <t>0.0036,0.0023,0.0004,0.9977</t>
+  </si>
+  <si>
+    <t>0.0020,0.0003,0.0018,0.9980</t>
+  </si>
+  <si>
+    <t>0.0005,0.9466,0.1231,0.0048</t>
+  </si>
+  <si>
+    <t>0.9939,0.0015,0.0013,0.0018</t>
+  </si>
+  <si>
+    <t>0.2537,0.8120,0.0026,0.0041</t>
+  </si>
+  <si>
+    <t>0.9959,0.0015,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.5935,0.5908,0.0049,0.0010</t>
+  </si>
+  <si>
+    <t>0.9887,0.0012,0.0029,0.0039</t>
+  </si>
+  <si>
+    <t>0.2655,0.0158,0.0036,0.7873</t>
+  </si>
+  <si>
+    <t>0.9899,0.0049,0.0006,0.0019</t>
+  </si>
+  <si>
+    <t>0.0037,0.0342,0.9800,0.0210</t>
+  </si>
+  <si>
+    <t>0.8993,0.0002,0.0012,0.1359</t>
+  </si>
+  <si>
+    <t>0.7981,0.0124,0.0124,0.2080</t>
+  </si>
+  <si>
+    <t>0.3598,0.6340,0.0452,0.0040</t>
+  </si>
+  <si>
+    <t>0.9432,0.0443,0.0094,0.0119</t>
+  </si>
+  <si>
+    <t>0.9543,0.0332,0.0123,0.0037</t>
+  </si>
+  <si>
+    <t>0.5424,0.5476,0.0058,0.0023</t>
+  </si>
+  <si>
+    <t>0.3732,0.2323,0.4630,0.0074</t>
+  </si>
+  <si>
+    <t>0.9699,0.0245,0.0031,0.0029</t>
+  </si>
+  <si>
+    <t>0.9970,0.0006,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9956,0.0012,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9943,0.0016,0.0008,0.0014</t>
+  </si>
+  <si>
+    <t>0.9920,0.0005,0.0004,0.0067</t>
+  </si>
+  <si>
+    <t>0.9973,0.0011,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9951,0.0010,0.0033,0.0003</t>
+  </si>
+  <si>
+    <t>0.9956,0.0020,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9936,0.0002,0.0001,0.0056</t>
+  </si>
+  <si>
+    <t>0.9332,0.1264,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.8840,0.1526,0.0113,0.0010</t>
+  </si>
+  <si>
+    <t>0.7969,0.3021,0.0095,0.0023</t>
+  </si>
+  <si>
+    <t>0.0425,0.6150,0.8049,0.0048</t>
+  </si>
+  <si>
+    <t>0.9743,0.0202,0.0073,0.0039</t>
+  </si>
+  <si>
+    <t>0.9687,0.0271,0.0078,0.0024</t>
+  </si>
+  <si>
+    <t>0.9859,0.0063,0.0053,0.0016</t>
+  </si>
+  <si>
+    <t>0.9878,0.0092,0.0010,0.0019</t>
+  </si>
+  <si>
+    <t>0.0014,0.0300,0.9941,0.0015</t>
+  </si>
+  <si>
+    <t>0.9695,0.0273,0.0063,0.0030</t>
+  </si>
+  <si>
+    <t>0.0010,0.0557,0.9921,0.0003</t>
+  </si>
+  <si>
+    <t>0.0410,0.0893,0.9454,0.0030</t>
+  </si>
+  <si>
+    <t>0.0048,0.0014,0.9930,0.0004</t>
+  </si>
+  <si>
+    <t>0.0634,0.1531,0.9197,0.0008</t>
+  </si>
+  <si>
+    <t>0.0164,0.0172,0.9760,0.0017</t>
+  </si>
+  <si>
+    <t>0.0037,0.0118,0.9930,0.0016</t>
+  </si>
+  <si>
+    <t>0.0079,0.0074,0.9877,0.0026</t>
+  </si>
+  <si>
+    <t>0.1498,0.0209,0.8660,0.0072</t>
+  </si>
+  <si>
+    <t>0.1453,0.0205,0.8593,0.0077</t>
+  </si>
+  <si>
+    <t>0.0757,0.0704,0.8728,0.0052</t>
+  </si>
+  <si>
+    <t>0.4372,0.1600,0.2228,0.0011</t>
+  </si>
+  <si>
+    <t>0.1475,0.1203,0.6255,0.0013</t>
+  </si>
+  <si>
+    <t>0.0278,0.2208,0.8884,0.0124</t>
+  </si>
+  <si>
+    <t>0.7881,0.0349,0.2515,0.0132</t>
+  </si>
+  <si>
+    <t>0.0718,0.0755,0.8660,0.0089</t>
+  </si>
+  <si>
+    <t>0.9692,0.0287,0.0075,0.0006</t>
+  </si>
+  <si>
+    <t>0.9608,0.0883,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9848,0.0154,0.0024,0.0010</t>
+  </si>
+  <si>
+    <t>0.9681,0.0537,0.0020,0.0010</t>
+  </si>
+  <si>
+    <t>0.9161,0.1154,0.0099,0.0088</t>
+  </si>
+  <si>
+    <t>0.6066,0.2563,0.1636,0.0118</t>
+  </si>
+  <si>
+    <t>0.7342,0.0027,0.4524,0.0023</t>
+  </si>
+  <si>
+    <t>0.9016,0.0195,0.0420,0.0222</t>
+  </si>
+  <si>
+    <t>0.1469,0.0181,0.8648,0.0093</t>
+  </si>
+  <si>
+    <t>0.4573,0.0540,0.5116,0.0400</t>
+  </si>
+  <si>
+    <t>0.0222,0.0109,0.9576,0.0115</t>
+  </si>
+  <si>
+    <t>0.0371,0.3364,0.8466,0.0030</t>
+  </si>
+  <si>
+    <t>0.0938,0.1023,0.8396,0.0862</t>
+  </si>
+  <si>
+    <t>0.1095,0.0179,0.8986,0.0004</t>
+  </si>
+  <si>
+    <t>0.0026,0.0045,0.9874,0.0020</t>
+  </si>
+  <si>
+    <t>0.9908,0.0011,0.0003,0.0048</t>
+  </si>
+  <si>
+    <t>0.9960,0.0021,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.9976,0.0011,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9954,0.0031,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9700,0.0356,0.0032,0.0017</t>
+  </si>
+  <si>
+    <t>0.9926,0.0046,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.9951,0.0019,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9982,0.0004,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.0248,0.0637,0.9599,0.0052</t>
+  </si>
+  <si>
+    <t>0.1043,0.5203,0.5443,0.0106</t>
+  </si>
+  <si>
+    <t>0.9667,0.0123,0.0173,0.0020</t>
+  </si>
+  <si>
+    <t>0.0004,0.0021,0.9958,0.0022</t>
+  </si>
+  <si>
+    <t>0.0015,0.0511,0.9854,0.0042</t>
+  </si>
+  <si>
+    <t>0.0045,0.2075,0.9651,0.0055</t>
+  </si>
+  <si>
+    <t>0.0132,0.0021,0.9906,0.0003</t>
+  </si>
+  <si>
+    <t>0.0128,0.0261,0.9751,0.0010</t>
+  </si>
+  <si>
+    <t>0.0047,0.0026,0.9959,0.0003</t>
+  </si>
+  <si>
+    <t>0.0226,0.0166,0.9611,0.0144</t>
+  </si>
+  <si>
+    <t>0.0859,0.2358,0.7833,0.0179</t>
+  </si>
+  <si>
+    <t>0.8402,0.0020,0.2566,0.0039</t>
+  </si>
+  <si>
+    <t>0.8916,0.0011,0.2425,0.0015</t>
+  </si>
+  <si>
+    <t>0.9731,0.0012,0.0297,0.0018</t>
+  </si>
+  <si>
+    <t>0.9937,0.0030,0.0011,0.0012</t>
+  </si>
+  <si>
+    <t>0.9983,0.0007,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9969,0.0014,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9948,0.0035,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.9981,0.0002,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9954,0.0043,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9833,0.0119,0.0014,0.0029</t>
+  </si>
+  <si>
+    <t>0.9979,0.0004,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.0033,0.1399,0.9621,0.0011</t>
+  </si>
+  <si>
+    <t>0.0040,0.0977,0.9786,0.0014</t>
+  </si>
+  <si>
+    <t>0.0057,0.0032,0.9895,0.0025</t>
+  </si>
+  <si>
+    <t>0.0383,0.0047,0.9632,0.0004</t>
+  </si>
+  <si>
+    <t>0.0195,0.0011,0.9891,0.0007</t>
+  </si>
+  <si>
+    <t>0.2812,0.0578,0.4610,0.2284</t>
+  </si>
+  <si>
+    <t>0.3151,0.0040,0.8342,0.0009</t>
+  </si>
+  <si>
+    <t>0.1019,0.0542,0.8569,0.0077</t>
+  </si>
+  <si>
+    <t>0.9536,0.0002,0.0004,0.0657</t>
+  </si>
+  <si>
+    <t>0.6811,0.0054,0.0206,0.3361</t>
+  </si>
+  <si>
+    <t>0.4267,0.0011,0.0019,0.7798</t>
+  </si>
+  <si>
+    <t>0.0040,0.0001,0.0010,0.9976</t>
+  </si>
+  <si>
+    <t>0.0032,0.0002,0.0013,0.9979</t>
+  </si>
+  <si>
+    <t>0.9417,0.0061,0.0214,0.0315</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2443,7 +2443,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2625,7 +2625,7 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
         <v>312</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2681,7 +2681,7 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
         <v>316</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2863,7 +2863,7 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D67" t="s">
         <v>329</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3395,7 +3395,7 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D105" t="s">
         <v>367</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3577,7 +3577,7 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
         <v>380</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
         <v>457</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4809,7 +4809,7 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
         <v>468</v>
@@ -4823,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
         <v>469</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5075,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
         <v>487</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5103,7 +5103,7 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D227" t="s">
         <v>489</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
